--- a/data/trans_orig/P36B14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016</t>
+          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>29112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53022</t>
+          <t>52628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48453</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76783</t>
+          <t>76428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82152</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121417</t>
+          <t>123061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62269</t>
+          <t>61415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51184</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68341</t>
+          <t>67623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103863</t>
+          <t>102231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61072</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>93576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69608</t>
+          <t>70884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103922</t>
+          <t>102830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140586</t>
+          <t>142862</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>186925</t>
+          <t>187462</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96678</t>
+          <t>95545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132524</t>
+          <t>132738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91360</t>
+          <t>92249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126370</t>
+          <t>127518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196974</t>
+          <t>197010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248139</t>
+          <t>246461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119862</t>
+          <t>119165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157720</t>
+          <t>160383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120245</t>
+          <t>119854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216380</t>
+          <t>217720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>268320</t>
+          <t>269901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66030</t>
+          <t>64795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100805</t>
+          <t>100310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91143</t>
+          <t>90972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128731</t>
+          <t>129115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167013</t>
+          <t>167125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215308</t>
+          <t>217380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54451</t>
+          <t>55165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85637</t>
+          <t>85949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67546</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99253</t>
+          <t>99372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128883</t>
+          <t>129390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178339</t>
+          <t>175379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106439</t>
+          <t>104566</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145303</t>
+          <t>143168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103694</t>
+          <t>103938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140365</t>
+          <t>143634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218751</t>
+          <t>217524</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>273020</t>
+          <t>269925</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150010</t>
+          <t>150624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193670</t>
+          <t>194541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108297</t>
+          <t>105923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145732</t>
+          <t>144829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266213</t>
+          <t>270222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329012</t>
+          <t>327109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124930</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165079</t>
+          <t>161695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106819</t>
+          <t>108356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145712</t>
+          <t>147576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240065</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296430</t>
+          <t>296559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119179</t>
+          <t>120458</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163204</t>
+          <t>164693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142717</t>
+          <t>140373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186939</t>
+          <t>183876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>270888</t>
+          <t>269970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>335113</t>
+          <t>329826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85509</t>
+          <t>86455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124810</t>
+          <t>122668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104739</t>
+          <t>106280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145994</t>
+          <t>145992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202117</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258623</t>
+          <t>257806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120240</t>
+          <t>121733</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162906</t>
+          <t>162093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>102712</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>142941</t>
+          <t>142016</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>235058</t>
+          <t>237406</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>292227</t>
+          <t>295868</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145098</t>
+          <t>146819</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>193502</t>
+          <t>189724</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106834</t>
+          <t>110343</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147346</t>
+          <t>150003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>265809</t>
+          <t>266934</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>329327</t>
+          <t>328085</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95760</t>
+          <t>93518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135250</t>
+          <t>135176</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102439</t>
+          <t>102919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142480</t>
+          <t>142316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206960</t>
+          <t>208901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264835</t>
+          <t>262754</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181421</t>
+          <t>181417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232429</t>
+          <t>227514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207521</t>
+          <t>206475</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>256979</t>
+          <t>256068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401631</t>
+          <t>401851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>471288</t>
+          <t>470646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106932</t>
+          <t>106593</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149468</t>
+          <t>149818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110379</t>
+          <t>107369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148537</t>
+          <t>148351</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227061</t>
+          <t>225940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>289241</t>
+          <t>282997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>107088</t>
+          <t>108742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150969</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101876</t>
+          <t>100732</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>140279</t>
+          <t>141094</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>220725</t>
+          <t>222763</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278438</t>
+          <t>281618</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74663</t>
+          <t>74351</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109675</t>
+          <t>109688</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79622</t>
+          <t>79607</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116261</t>
+          <t>115990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161483</t>
+          <t>161218</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>214441</t>
+          <t>212952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76004</t>
+          <t>77197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114926</t>
+          <t>113718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53262</t>
+          <t>54662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87463</t>
+          <t>86835</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137437</t>
+          <t>137572</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186408</t>
+          <t>187399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199194</t>
+          <t>198391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245454</t>
+          <t>244875</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226353</t>
+          <t>227492</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>272182</t>
+          <t>272964</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437292</t>
+          <t>437048</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>503706</t>
+          <t>503041</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77579</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113277</t>
+          <t>115482</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69886</t>
+          <t>69399</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104005</t>
+          <t>105894</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>158015</t>
+          <t>158291</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>210967</t>
+          <t>208782</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62953</t>
+          <t>62798</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95667</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58088</t>
+          <t>57265</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92230</t>
+          <t>93869</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>128561</t>
+          <t>132310</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>176408</t>
+          <t>180927</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40624</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>68653</t>
+          <t>69930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>43935</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>74831</t>
+          <t>73345</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>92149</t>
+          <t>92712</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>134547</t>
+          <t>134244</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30815</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32992</t>
+          <t>33299</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>64061</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>180267</t>
+          <t>180558</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>216309</t>
+          <t>218378</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>206959</t>
+          <t>204305</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>244705</t>
+          <t>243684</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>396843</t>
+          <t>398932</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>452817</t>
+          <t>451639</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>43862</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>72170</t>
+          <t>71827</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>57018</t>
+          <t>57290</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>88957</t>
+          <t>88378</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>111407</t>
+          <t>109699</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>152810</t>
+          <t>152752</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>60690</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34541</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60336</t>
+          <t>60872</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>74967</t>
+          <t>75116</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>111698</t>
+          <t>109282</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>27922</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>31325</t>
+          <t>32028</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>57074</t>
+          <t>57449</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>18103</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29387</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>165757</t>
+          <t>164749</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>191004</t>
+          <t>189996</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>240551</t>
+          <t>240513</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>282430</t>
+          <t>283048</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>418009</t>
+          <t>416363</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>467258</t>
+          <t>464115</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24122</t>
+          <t>23796</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>42297</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>44346</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>77088</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>74866</t>
+          <t>74574</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>112963</t>
+          <t>113761</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28733</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>48187</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>41217</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>70606</t>
+          <t>69831</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>44551</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>12535</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31944</t>
+          <t>30221</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1009521</t>
+          <t>1016057</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1121586</t>
+          <t>1124840</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1236228</t>
+          <t>1241152</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1357265</t>
+          <t>1357914</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2289214</t>
+          <t>2291401</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2439943</t>
+          <t>2452599</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>488272</t>
+          <t>493512</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>579916</t>
+          <t>579744</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>541441</t>
+          <t>541756</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>631440</t>
+          <t>632915</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1055100</t>
+          <t>1060499</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1185675</t>
+          <t>1183688</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>569173</t>
+          <t>572154</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>661902</t>
+          <t>665401</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>559677</t>
+          <t>563244</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>651913</t>
+          <t>652079</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1163119</t>
+          <t>1161984</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1285691</t>
+          <t>1295175</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>586150</t>
+          <t>582041</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>674847</t>
+          <t>677375</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>520070</t>
+          <t>514636</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>609413</t>
+          <t>608232</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1127649</t>
+          <t>1130901</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1254806</t>
+          <t>1254060</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>483864</t>
+          <t>481946</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>572674</t>
+          <t>570117</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>430332</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>509047</t>
+          <t>507796</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>935650</t>
+          <t>933163</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1053818</t>
+          <t>1049478</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52628</t>
+          <t>53876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76428</t>
+          <t>76258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>84709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123061</t>
+          <t>120822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>34925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61415</t>
+          <t>62041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,82 +858,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>36723</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26497</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>49030</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>84021</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>67604</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>102777</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36723</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27719</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>49579</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>84021</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>67623</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>102231</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61580</t>
+          <t>61272</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93576</t>
+          <t>93886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70884</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102830</t>
+          <t>102502</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>142862</t>
+          <t>141226</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>187462</t>
+          <t>186357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95545</t>
+          <t>97047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132738</t>
+          <t>133970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92249</t>
+          <t>89951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127518</t>
+          <t>124861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197010</t>
+          <t>196240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246461</t>
+          <t>246958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119165</t>
+          <t>120813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160383</t>
+          <t>159302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85429</t>
+          <t>88429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119854</t>
+          <t>121592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>217720</t>
+          <t>218142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269901</t>
+          <t>270207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64795</t>
+          <t>65677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100310</t>
+          <t>100112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90972</t>
+          <t>90826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129115</t>
+          <t>127242</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167125</t>
+          <t>162911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217380</t>
+          <t>214787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55165</t>
+          <t>52660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85949</t>
+          <t>85226</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>67064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99372</t>
+          <t>98577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129390</t>
+          <t>131161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175379</t>
+          <t>178120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104566</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143168</t>
+          <t>144009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103938</t>
+          <t>103544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143634</t>
+          <t>140633</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>217524</t>
+          <t>219123</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269925</t>
+          <t>271024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150624</t>
+          <t>151532</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194541</t>
+          <t>197408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105923</t>
+          <t>106455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144829</t>
+          <t>146193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>270222</t>
+          <t>270022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>327109</t>
+          <t>328055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121530</t>
+          <t>123667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161695</t>
+          <t>165633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108356</t>
+          <t>108553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147576</t>
+          <t>147151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>241546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296559</t>
+          <t>297142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120458</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>164693</t>
+          <t>160452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140373</t>
+          <t>142411</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183876</t>
+          <t>186338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269970</t>
+          <t>272788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>329826</t>
+          <t>334501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86455</t>
+          <t>86938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122668</t>
+          <t>125823</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106280</t>
+          <t>103574</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145992</t>
+          <t>145287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>200714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257806</t>
+          <t>258026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121733</t>
+          <t>122389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162093</t>
+          <t>164406</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102712</t>
+          <t>103586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>142016</t>
+          <t>141969</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>237406</t>
+          <t>234527</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295868</t>
+          <t>292294</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146819</t>
+          <t>146322</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>189724</t>
+          <t>191656</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110343</t>
+          <t>110254</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>150003</t>
+          <t>150050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>266934</t>
+          <t>264496</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>328085</t>
+          <t>327772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93518</t>
+          <t>96904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>133275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102919</t>
+          <t>103241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142316</t>
+          <t>141840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>208901</t>
+          <t>209366</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>262754</t>
+          <t>264263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181417</t>
+          <t>182200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>227514</t>
+          <t>232388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>206475</t>
+          <t>206372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>256068</t>
+          <t>257112</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401851</t>
+          <t>403861</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470646</t>
+          <t>473397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106593</t>
+          <t>108863</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149818</t>
+          <t>150153</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107369</t>
+          <t>106781</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>148695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225940</t>
+          <t>226341</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282997</t>
+          <t>287551</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108742</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>152513</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100732</t>
+          <t>96053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>141094</t>
+          <t>140595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>222763</t>
+          <t>221646</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>281618</t>
+          <t>277662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74351</t>
+          <t>73160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>109265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79607</t>
+          <t>79471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115990</t>
+          <t>116736</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161218</t>
+          <t>164759</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212952</t>
+          <t>215744</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>76347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113718</t>
+          <t>112370</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86835</t>
+          <t>87131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137572</t>
+          <t>139523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>187399</t>
+          <t>190644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198391</t>
+          <t>200564</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>244875</t>
+          <t>244243</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>227492</t>
+          <t>224054</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>272964</t>
+          <t>273238</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437048</t>
+          <t>436508</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>503041</t>
+          <t>501892</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>77580</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115482</t>
+          <t>114497</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69399</t>
+          <t>68437</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>105805</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>158291</t>
+          <t>158883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>208782</t>
+          <t>207095</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62798</t>
+          <t>63404</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>98236</t>
+          <t>95771</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57265</t>
+          <t>58486</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93869</t>
+          <t>95187</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132310</t>
+          <t>128132</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>180927</t>
+          <t>178724</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>40583</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>69930</t>
+          <t>69849</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43935</t>
+          <t>42863</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>73345</t>
+          <t>73970</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>92712</t>
+          <t>91795</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>134244</t>
+          <t>133915</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30815</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>40998</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>180558</t>
+          <t>181454</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>218378</t>
+          <t>216774</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>204305</t>
+          <t>206112</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>243684</t>
+          <t>247183</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>398932</t>
+          <t>397654</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>451639</t>
+          <t>453168</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>43862</t>
+          <t>45608</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>71827</t>
+          <t>73480</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>57290</t>
+          <t>55926</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>88378</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>109699</t>
+          <t>109036</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>152752</t>
+          <t>151136</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>34149</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>59789</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>32826</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60872</t>
+          <t>58984</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>75116</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>109282</t>
+          <t>111997</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>26998</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>36762</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>32028</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>57449</t>
+          <t>56896</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11755</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>30057</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>164749</t>
+          <t>165377</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>189835</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>240513</t>
+          <t>240766</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>283048</t>
+          <t>282382</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>416363</t>
+          <t>415603</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>464115</t>
+          <t>464947</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>43765</t>
+          <t>45648</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>77088</t>
+          <t>77352</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>74423</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>113761</t>
+          <t>110770</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>23367</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>47540</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>39846</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>69831</t>
+          <t>70311</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17817</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21574</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>45047</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1016057</t>
+          <t>1013835</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1124840</t>
+          <t>1124029</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1241152</t>
+          <t>1239405</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1357914</t>
+          <t>1356050</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2291401</t>
+          <t>2288910</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2452599</t>
+          <t>2445072</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>493512</t>
+          <t>487730</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>579744</t>
+          <t>580383</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>541756</t>
+          <t>545281</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>632915</t>
+          <t>631415</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1060499</t>
+          <t>1052328</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1183688</t>
+          <t>1181943</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>572154</t>
+          <t>571734</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>665401</t>
+          <t>662270</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>563244</t>
+          <t>558737</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>652079</t>
+          <t>652614</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1161984</t>
+          <t>1160180</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1295175</t>
+          <t>1285395</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>582041</t>
+          <t>582847</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>677375</t>
+          <t>676407</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>514636</t>
+          <t>522344</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>608232</t>
+          <t>610335</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1130901</t>
+          <t>1125167</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1254060</t>
+          <t>1253831</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>481946</t>
+          <t>484555</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>567761</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>429255</t>
+          <t>429029</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>507796</t>
+          <t>507925</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>933163</t>
+          <t>931751</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1049478</t>
+          <t>1054926</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
